--- a/static/files/emp_info_sample.xlsx
+++ b/static/files/emp_info_sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desicrew\flask\Dmax\static\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDE35F8-F3E7-428B-A23A-23D1AA5F435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E00C25-7B19-4D1A-84DF-5E3417892970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3209FD0D-3AD8-4DC0-8EBB-917F5EF3BAE6}"/>
   </bookViews>
@@ -613,11 +613,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D2" xr:uid="{99586997-75A6-4018-A964-9068B2B1BEDB}">
-      <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E2" xr:uid="{A48CA42F-D9A3-43B6-AA0C-38492BCFE116}">
       <formula1>"Intern,Jr.QA Engineer,QA Engineer,Sr.QA Engineer,QA Lead"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{C1329A34-B5BA-49A6-824A-1031A45FB1BB}">
+      <formula1>"Akyrian,Auxo,Avanti,Bench,Fora Travels,Indihood,IPS,IQHive,LevelBlue,Web Development,Opus Clip,Training,Heymax,Trademo,ONECLICKLCA"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
